--- a/Trans To Vostok/Korean/Images.xlsx
+++ b/Trans To Vostok/Korean/Images.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SteamLibrary\steamapps\common\Road to Vostok\mods\Trans To Vostok\Korean\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SteamLibrary\steamapps\common\Road to Vostok\mods\Trans To Vostok\Trans To Vostok\Korean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7A4BFB-A16D-4739-8204-30FB913F25B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80801F4-D229-437A-BE2B-D75E4D4E143D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{E0CAA4CC-5EC0-4298-9780-F39DB2CE6684}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{E0CAA4CC-5EC0-4298-9780-F39DB2CE6684}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tutorial" sheetId="1" r:id="rId1"/>
+    <sheet name="UI" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="91">
   <si>
     <t>Tutorial</t>
   </si>
@@ -68,23 +69,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>text</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>translation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Where</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Sub</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -599,12 +588,89 @@
 영구 사망 해골 아이콘이 나타납니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Map</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Worldmap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI\Sprites</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>World_Map.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reworked by</t>
+  </si>
+  <si>
+    <t>Reworked by</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MuteJack</t>
+  </si>
+  <si>
+    <t>MuteJack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Permadeath Skull Icon: https://pixabay.com/ko/photos/%eb%91%90%ea%b0%9c%ea%b3%a8-%ea%b3%b5%ed%8f%ac-%ed%95%b4%ea%b3%a8-8964071/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Performance Icon: Hand-crafted (Reconstruction)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attribution</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>File Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>File Directory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Text</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aerial Image: Copernicus Sentinel data 2026, processed with Corpernicus Browser
+Crumpled Paper: Pixabay (https://pixabay.com/ko/photos/%ea%b5%ac%ea%b2%a8%ec%a7%84-%ec%a2%85%ec%9d%b4-%eb%b8%94%eb%9e%99-%ec%a2%85%ec%9d%b4-6793287/)
+Airplane Icon: Pixabay (https://pixabay.com/vectors/airplane-)transportation-symbol-icon-23997/
+Masking Tape: Texturelabs (https://texturelabs.org/textures/details_122/)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,21 +697,56 @@
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -654,27 +755,36 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1010,402 +1120,669 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88310B32-1EF1-4265-A60F-0339C38439EB}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="3" max="3" width="12.59765625" customWidth="1"/>
+    <col min="1" max="2" width="8.796875" style="2"/>
+    <col min="3" max="3" width="12.59765625" style="2" customWidth="1"/>
     <col min="4" max="4" width="56.296875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="66.5" customWidth="1"/>
-    <col min="6" max="6" width="58.296875" customWidth="1"/>
-    <col min="7" max="7" width="69.296875" customWidth="1"/>
+    <col min="5" max="5" width="66.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="58.296875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="69.296875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.3984375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="53.19921875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="5" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="B1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7" ht="261">
-      <c r="A2" s="4" t="s">
+      <c r="C1" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="261">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="208.8">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="261">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="243.6">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="261">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="278.39999999999998">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="313.2">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="261">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="261">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="400.2">
+      <c r="A11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="261">
+      <c r="A12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="261">
+      <c r="A13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="208.8">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="261">
-      <c r="A4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="243.6">
-      <c r="A5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="261">
-      <c r="A6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="H13" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="261">
+      <c r="A14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="278.39999999999998">
+      <c r="A15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="243.6">
+      <c r="A16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="278.39999999999998">
-      <c r="A7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="313.2">
-      <c r="A8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="261">
-      <c r="A9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="261">
-      <c r="A10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="400.2">
-      <c r="A11" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="261">
-      <c r="A12" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="E16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="261">
+      <c r="A17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="261">
-      <c r="A13" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="261">
-      <c r="A14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="E17" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="278.39999999999998">
-      <c r="A15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="H17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61281094-5A26-43DB-B173-C8F47C01DA95}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="2" width="8.796875" style="2"/>
+    <col min="3" max="3" width="12.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.296875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="66.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="58.296875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="69.296875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.3984375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="53.19921875" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="174">
+      <c r="A2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="243.6">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="261">
-      <c r="A17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="D2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="D14" s="4"/>
+      <c r="E14" s="5"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="D15" s="4"/>
+      <c r="E15" s="5"/>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="C16" s="1"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="3:7">
+      <c r="C17" s="1"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5"/>
+      <c r="G17" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
